--- a/Team-Data/2012-13/11-29-2012-13.xlsx
+++ b/Team-Data/2012-13/11-29-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,13 +806,13 @@
         <v>3.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
       </c>
       <c r="AF2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG2" t="n">
         <v>7</v>
@@ -754,7 +821,7 @@
         <v>17</v>
       </c>
       <c r="AI2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ2" t="n">
         <v>17</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -921,10 +988,10 @@
         <v>-1.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF3" t="n">
         <v>12</v>
@@ -936,7 +1003,7 @@
         <v>9</v>
       </c>
       <c r="AI3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ3" t="n">
         <v>27</v>
@@ -957,7 +1024,7 @@
         <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ3" t="n">
         <v>3</v>
@@ -993,7 +1060,7 @@
         <v>19</v>
       </c>
       <c r="BB3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -1103,19 +1170,19 @@
         <v>4.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG4" t="n">
         <v>5</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI4" t="n">
         <v>20</v>
@@ -1130,7 +1197,7 @@
         <v>14</v>
       </c>
       <c r="AM4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN4" t="n">
         <v>22</v>
@@ -1154,7 +1221,7 @@
         <v>11</v>
       </c>
       <c r="AU4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV4" t="n">
         <v>4</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
         <v>14</v>
@@ -1294,7 +1361,7 @@
         <v>12</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
         <v>3</v>
@@ -1309,13 +1376,13 @@
         <v>29</v>
       </c>
       <c r="AL5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO5" t="n">
         <v>3</v>
@@ -1339,7 +1406,7 @@
         <v>30</v>
       </c>
       <c r="AV5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW5" t="n">
         <v>4</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
         <v>14</v>
@@ -1476,10 +1543,10 @@
         <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
         <v>21</v>
@@ -1503,7 +1570,7 @@
         <v>8</v>
       </c>
       <c r="AP6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
         <v>4</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-5.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
@@ -1673,7 +1740,7 @@
         <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM7" t="n">
         <v>6</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>14</v>
@@ -1843,7 +1910,7 @@
         <v>20</v>
       </c>
       <c r="AH8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI8" t="n">
         <v>15</v>
@@ -1852,19 +1919,19 @@
         <v>18</v>
       </c>
       <c r="AK8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL8" t="n">
         <v>7</v>
       </c>
       <c r="AM8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN8" t="n">
         <v>5</v>
       </c>
       <c r="AO8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP8" t="n">
         <v>17</v>
@@ -1876,13 +1943,13 @@
         <v>27</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
         <v>21</v>
       </c>
       <c r="AU8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV8" t="n">
         <v>15</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -1935,22 +2002,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="H9" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I9" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="J9" t="n">
         <v>85.3</v>
@@ -1959,76 +2026,76 @@
         <v>0.455</v>
       </c>
       <c r="L9" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.329</v>
+        <v>0.318</v>
       </c>
       <c r="O9" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="P9" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.674</v>
+        <v>0.666</v>
       </c>
       <c r="R9" t="n">
-        <v>15.1</v>
+        <v>15.5</v>
       </c>
       <c r="S9" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T9" t="n">
-        <v>46.8</v>
+        <v>47.3</v>
       </c>
       <c r="U9" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="V9" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="W9" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X9" t="n">
         <v>6.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB9" t="n">
-        <v>99.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF9" t="n">
         <v>12</v>
       </c>
-      <c r="AF9" t="n">
-        <v>16</v>
-      </c>
       <c r="AG9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AI9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ9" t="n">
         <v>3</v>
@@ -2037,13 +2104,13 @@
         <v>6</v>
       </c>
       <c r="AL9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AM9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
         <v>23</v>
@@ -2052,25 +2119,25 @@
         <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR9" t="n">
         <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
         <v>2</v>
       </c>
       <c r="AU9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AV9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
         <v>6</v>
@@ -2082,10 +2149,10 @@
         <v>12</v>
       </c>
       <c r="BA9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BC9" t="n">
         <v>12</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2228,7 +2295,7 @@
         <v>6</v>
       </c>
       <c r="AO10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP10" t="n">
         <v>8</v>
@@ -2255,16 +2322,16 @@
         <v>27</v>
       </c>
       <c r="AX10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ10" t="n">
         <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB10" t="n">
         <v>19</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -2299,121 +2366,121 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
         <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6</v>
+        <v>0.571</v>
       </c>
       <c r="H11" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="I11" t="n">
-        <v>37.3</v>
+        <v>36.8</v>
       </c>
       <c r="J11" t="n">
-        <v>82.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.45</v>
+        <v>0.446</v>
       </c>
       <c r="L11" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M11" t="n">
         <v>19.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.332</v>
+        <v>0.325</v>
       </c>
       <c r="O11" t="n">
-        <v>17.7</v>
+        <v>18.2</v>
       </c>
       <c r="P11" t="n">
-        <v>23.7</v>
+        <v>24.4</v>
       </c>
       <c r="Q11" t="n">
         <v>0.746</v>
       </c>
       <c r="R11" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="S11" t="n">
         <v>33.9</v>
       </c>
       <c r="T11" t="n">
-        <v>45.7</v>
+        <v>45.9</v>
       </c>
       <c r="U11" t="n">
-        <v>21.7</v>
+        <v>21.1</v>
       </c>
       <c r="V11" t="n">
         <v>16.4</v>
       </c>
       <c r="W11" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="X11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Y11" t="n">
         <v>6.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>21</v>
+        <v>21.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.5</v>
+        <v>98</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AE11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AF11" t="n">
         <v>8</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AP11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AQ11" t="n">
         <v>19</v>
@@ -2428,16 +2495,16 @@
         <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AV11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW11" t="n">
         <v>26</v>
       </c>
       <c r="AX11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY11" t="n">
         <v>24</v>
@@ -2446,10 +2513,10 @@
         <v>27</v>
       </c>
       <c r="BA11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BB11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BC11" t="n">
         <v>15</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -2559,13 +2626,13 @@
         <v>0.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
         <v>14</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG12" t="n">
         <v>17</v>
@@ -2628,7 +2695,7 @@
         <v>8</v>
       </c>
       <c r="BA12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB12" t="n">
         <v>5</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -2741,19 +2808,19 @@
         <v>-0.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
         <v>14</v>
       </c>
       <c r="AF13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG13" t="n">
         <v>17</v>
       </c>
       <c r="AH13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
@@ -2771,7 +2838,7 @@
         <v>13</v>
       </c>
       <c r="AN13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
         <v>18</v>
@@ -2810,7 +2877,7 @@
         <v>7</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>4.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE14" t="n">
         <v>7</v>
@@ -2938,7 +3005,7 @@
         <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ14" t="n">
         <v>26</v>
@@ -2959,7 +3026,7 @@
         <v>10</v>
       </c>
       <c r="AP14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
         <v>14</v>
@@ -2974,7 +3041,7 @@
         <v>26</v>
       </c>
       <c r="AU14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV14" t="n">
         <v>25</v>
@@ -2992,10 +3059,10 @@
         <v>30</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC14" t="n">
         <v>7</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3172,13 @@
         <v>3.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
         <v>14</v>
       </c>
       <c r="AF15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG15" t="n">
         <v>17</v>
@@ -3129,7 +3196,7 @@
         <v>8</v>
       </c>
       <c r="AL15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM15" t="n">
         <v>7</v>
@@ -3144,7 +3211,7 @@
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR15" t="n">
         <v>8</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>8.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3302,13 +3369,13 @@
         <v>26</v>
       </c>
       <c r="AI16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ16" t="n">
         <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL16" t="n">
         <v>23</v>
@@ -3338,10 +3405,10 @@
         <v>16</v>
       </c>
       <c r="AU16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AV16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW16" t="n">
         <v>2</v>
@@ -3359,7 +3426,7 @@
         <v>3</v>
       </c>
       <c r="BB16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC16" t="n">
         <v>2</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -3391,73 +3458,73 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>0.786</v>
+        <v>0.769</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>39</v>
+        <v>38.8</v>
       </c>
       <c r="J17" t="n">
-        <v>79</v>
+        <v>78.5</v>
       </c>
       <c r="K17" t="n">
         <v>0.494</v>
       </c>
       <c r="L17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="M17" t="n">
-        <v>20.4</v>
+        <v>21</v>
       </c>
       <c r="N17" t="n">
-        <v>0.43</v>
+        <v>0.432</v>
       </c>
       <c r="O17" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="P17" t="n">
-        <v>23.7</v>
+        <v>24.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.759</v>
+        <v>0.754</v>
       </c>
       <c r="R17" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="S17" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T17" t="n">
-        <v>39.4</v>
+        <v>39.6</v>
       </c>
       <c r="U17" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="V17" t="n">
-        <v>14.1</v>
+        <v>14.5</v>
       </c>
       <c r="W17" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="X17" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA17" t="n">
         <v>20.8</v>
@@ -3469,22 +3536,22 @@
         <v>4.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF17" t="n">
         <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ17" t="n">
         <v>25</v>
@@ -3496,19 +3563,19 @@
         <v>3</v>
       </c>
       <c r="AM17" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AN17" t="n">
         <v>1</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3517,25 +3584,25 @@
         <v>11</v>
       </c>
       <c r="AT17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU17" t="n">
         <v>4</v>
       </c>
       <c r="AV17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AW17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AX17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY17" t="n">
         <v>3</v>
       </c>
       <c r="AZ17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA17" t="n">
         <v>14</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
         <v>14</v>
@@ -3705,7 +3772,7 @@
         <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW18" t="n">
         <v>10</v>
@@ -3723,7 +3790,7 @@
         <v>27</v>
       </c>
       <c r="BB18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC18" t="n">
         <v>14</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>-0.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
         <v>22</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-5.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE20" t="n">
         <v>26</v>
@@ -4066,10 +4133,10 @@
         <v>22</v>
       </c>
       <c r="AU20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW20" t="n">
         <v>30</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -4197,25 +4264,25 @@
         <v>7.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG21" t="n">
         <v>5</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="n">
         <v>9</v>
@@ -4272,7 +4339,7 @@
         <v>4</v>
       </c>
       <c r="BC21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -4379,22 +4446,22 @@
         <v>9</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG22" t="n">
         <v>4</v>
       </c>
       <c r="AH22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
         <v>30</v>
@@ -4436,7 +4503,7 @@
         <v>28</v>
       </c>
       <c r="AW22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE23" t="n">
         <v>24</v>
@@ -4573,7 +4640,7 @@
         <v>24</v>
       </c>
       <c r="AH23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI23" t="n">
         <v>16</v>
@@ -4612,7 +4679,7 @@
         <v>8</v>
       </c>
       <c r="AU23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV23" t="n">
         <v>21</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
         <v>7</v>
@@ -4782,7 +4849,7 @@
         <v>27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR24" t="n">
         <v>23</v>
@@ -4794,13 +4861,13 @@
         <v>17</v>
       </c>
       <c r="AU24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
       </c>
       <c r="AW24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-4.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -4937,7 +5004,7 @@
         <v>20</v>
       </c>
       <c r="AH25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI25" t="n">
         <v>5</v>
@@ -4949,7 +5016,7 @@
         <v>16</v>
       </c>
       <c r="AL25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM25" t="n">
         <v>24</v>
@@ -4997,7 +5064,7 @@
         <v>21</v>
       </c>
       <c r="BB25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC25" t="n">
         <v>23</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE26" t="n">
         <v>22</v>
@@ -5137,7 +5204,7 @@
         <v>3</v>
       </c>
       <c r="AN26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO26" t="n">
         <v>20</v>
@@ -5161,7 +5228,7 @@
         <v>26</v>
       </c>
       <c r="AV26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW26" t="n">
         <v>9</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-5.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
@@ -5304,7 +5371,7 @@
         <v>7</v>
       </c>
       <c r="AI27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ27" t="n">
         <v>5</v>
@@ -5337,7 +5404,7 @@
         <v>28</v>
       </c>
       <c r="AT27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -5393,82 +5460,82 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E28" t="n">
         <v>13</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>0.765</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
       </c>
       <c r="I28" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="J28" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K28" t="n">
-        <v>0.479</v>
+        <v>0.481</v>
       </c>
       <c r="L28" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M28" t="n">
-        <v>21.4</v>
+        <v>20.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.372</v>
+        <v>0.375</v>
       </c>
       <c r="O28" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P28" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="R28" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T28" t="n">
-        <v>41.1</v>
+        <v>40.8</v>
       </c>
       <c r="U28" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="V28" t="n">
-        <v>15.1</v>
+        <v>14.8</v>
       </c>
       <c r="W28" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X28" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.4</v>
+        <v>102.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="AD28" t="n">
         <v>1</v>
@@ -5477,31 +5544,31 @@
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK28" t="n">
         <v>3</v>
       </c>
       <c r="AL28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AN28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO28" t="n">
         <v>22</v>
@@ -5510,7 +5577,7 @@
         <v>23</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR28" t="n">
         <v>28</v>
@@ -5519,34 +5586,34 @@
         <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY28" t="n">
         <v>19</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>16</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BB28" t="n">
         <v>3</v>
       </c>
       <c r="BC28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE29" t="n">
         <v>28</v>
@@ -5680,13 +5747,13 @@
         <v>13</v>
       </c>
       <c r="AM29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN29" t="n">
         <v>19</v>
       </c>
       <c r="AO29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP29" t="n">
         <v>17</v>
@@ -5701,7 +5768,7 @@
         <v>22</v>
       </c>
       <c r="AT29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>1.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
         <v>7</v>
@@ -5853,7 +5920,7 @@
         <v>18</v>
       </c>
       <c r="AJ30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK30" t="n">
         <v>23</v>
@@ -5874,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR30" t="n">
         <v>2</v>
@@ -5898,7 +5965,7 @@
         <v>4</v>
       </c>
       <c r="AY30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ30" t="n">
         <v>24</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-7.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE31" t="n">
         <v>30</v>
@@ -6077,16 +6144,16 @@
         <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ31" t="n">
         <v>25</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB31" t="n">
         <v>30</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-29-2012-13</t>
+          <t>2012-11-29</t>
         </is>
       </c>
     </row>
